--- a/A1_nodos_subnodos.xlsx
+++ b/A1_nodos_subnodos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a6e3a3034f87b97d/PROYECTO DE GRADO/Repositorio GITHUB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{34F95157-7C6C-4790-81FB-98ED2E3BAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED978AF5-9EFD-4226-A074-42ED0954432C}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{34F95157-7C6C-4790-81FB-98ED2E3BAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A21682-816E-4F9E-B35D-E29E5DE6D51F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{93BFAC3A-A64C-41DD-9C7B-7A768146236B}"/>
   </bookViews>
@@ -445,7 +445,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="E372" authorId="43" shapeId="0" xr:uid="{361E5AC9-792E-4D88-9E30-F522BE3016C6}">
+    <comment ref="E369" authorId="43" shapeId="0" xr:uid="{361E5AC9-792E-4D88-9E30-F522BE3016C6}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -453,7 +453,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="E373" authorId="44" shapeId="0" xr:uid="{FA5774CF-DDEF-4D00-818C-1C6BA1914343}">
+    <comment ref="E370" authorId="44" shapeId="0" xr:uid="{FA5774CF-DDEF-4D00-818C-1C6BA1914343}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -461,7 +461,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="E374" authorId="45" shapeId="0" xr:uid="{1C9A6531-14E2-43E1-A415-9922C3A9DA1C}">
+    <comment ref="E371" authorId="45" shapeId="0" xr:uid="{1C9A6531-14E2-43E1-A415-9922C3A9DA1C}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -469,7 +469,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="E386" authorId="46" shapeId="0" xr:uid="{B8E65C02-E5F0-437B-BA57-C86D4531CEBD}">
+    <comment ref="E383" authorId="46" shapeId="0" xr:uid="{B8E65C02-E5F0-437B-BA57-C86D4531CEBD}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -477,7 +477,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="E387" authorId="47" shapeId="0" xr:uid="{64839722-2100-496D-B29F-FF569669A4C7}">
+    <comment ref="E384" authorId="47" shapeId="0" xr:uid="{64839722-2100-496D-B29F-FF569669A4C7}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -485,7 +485,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="E391" authorId="48" shapeId="0" xr:uid="{F2DA0235-30F6-4246-A4EE-B32CF803333B}">
+    <comment ref="E388" authorId="48" shapeId="0" xr:uid="{F2DA0235-30F6-4246-A4EE-B32CF803333B}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -493,7 +493,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="D394" authorId="49" shapeId="0" xr:uid="{A3F8D0A1-2896-44F3-98D4-FFC3D1FEDB3B}">
+    <comment ref="D391" authorId="49" shapeId="0" xr:uid="{A3F8D0A1-2896-44F3-98D4-FFC3D1FEDB3B}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -501,7 +501,7 @@
     bARRERA</t>
       </text>
     </comment>
-    <comment ref="E395" authorId="50" shapeId="0" xr:uid="{892757C9-6B28-427F-A237-1C67F9F5A22E}">
+    <comment ref="E392" authorId="50" shapeId="0" xr:uid="{892757C9-6B28-427F-A237-1C67F9F5A22E}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -509,7 +509,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="E428" authorId="51" shapeId="0" xr:uid="{37736932-EE25-4985-9F3C-5296BFE6712C}">
+    <comment ref="E425" authorId="51" shapeId="0" xr:uid="{37736932-EE25-4985-9F3C-5296BFE6712C}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -517,7 +517,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="E430" authorId="52" shapeId="0" xr:uid="{C4595140-A80D-4537-B5D0-2F070260A2E2}">
+    <comment ref="E427" authorId="52" shapeId="0" xr:uid="{C4595140-A80D-4537-B5D0-2F070260A2E2}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -525,7 +525,7 @@
     BARRERA</t>
       </text>
     </comment>
-    <comment ref="E431" authorId="53" shapeId="0" xr:uid="{E31F43AA-26B0-425C-8DB9-2B88EEAA07A2}">
+    <comment ref="E428" authorId="53" shapeId="0" xr:uid="{E31F43AA-26B0-425C-8DB9-2B88EEAA07A2}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -533,7 +533,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="E440" authorId="54" shapeId="0" xr:uid="{53546CAF-F21F-4EEE-B5BA-BE3A63E66220}">
+    <comment ref="E437" authorId="54" shapeId="0" xr:uid="{53546CAF-F21F-4EEE-B5BA-BE3A63E66220}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -541,7 +541,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="E447" authorId="55" shapeId="0" xr:uid="{68A2B69D-EF21-4A73-A254-944BC17354BD}">
+    <comment ref="E444" authorId="55" shapeId="0" xr:uid="{68A2B69D-EF21-4A73-A254-944BC17354BD}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -549,7 +549,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="D451" authorId="56" shapeId="0" xr:uid="{9E3CDE71-45AD-4843-BF33-AC331DAC95BA}">
+    <comment ref="D448" authorId="56" shapeId="0" xr:uid="{9E3CDE71-45AD-4843-BF33-AC331DAC95BA}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -557,7 +557,7 @@
     Barrera</t>
       </text>
     </comment>
-    <comment ref="D484" authorId="57" shapeId="0" xr:uid="{987AFB11-BA69-415B-B7D3-8CD963274F50}">
+    <comment ref="D481" authorId="57" shapeId="0" xr:uid="{987AFB11-BA69-415B-B7D3-8CD963274F50}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -570,7 +570,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="1217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2580" uniqueCount="1210">
   <si>
     <t>Texto original (tal como aparece)</t>
   </si>
@@ -4363,30 +4363,6 @@
     <t xml:space="preserve">UNIVERSIDAD Y EMPRESA. Las teorías del derecho y la regulación influyen en los marcos legales y regulatorios, que reconocen el valor de un marco legal estructurado para controlar las relaciones universidad-industria (Awasthy et al., 2020). </t>
   </si>
   <si>
-    <t xml:space="preserve"> Transparencia en el proceso de vinculación </t>
-  </si>
-  <si>
-    <t>Meritocracia</t>
-  </si>
-  <si>
-    <t>UNIVERSIDAD Y EMPRESA. Implementación de políticas y actividades que aseguren la transparencia en el uso de recursos en proyectos de vinculación.</t>
-  </si>
-  <si>
-    <t>Practicas de gestión meritocraticas
-Meritocracia de los directivos</t>
-  </si>
-  <si>
-    <t>EMPRESA. Como la empresa maneja la productividad, lo ideal a base del rendimiento y la meritocracia. las prácticas de gestión meritocráticas inciden positivamente en el nexo universidad-empresa en Alemania, Francia y el Reino Unido, mientras que dichas prácticas no repercuten en la colaboración en I+D en Italia ni en España.
-Si en la empresas la selección y bonificacion de los empleados se da en base a la meritocracia de cada uno, se aumenta la probabilidad de colaborar en un entorno academico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mejores practicas de gestión 
-Practicas de gestion meritocratica </t>
-  </si>
-  <si>
-    <t>UNIVERSIDAD Y EMPRESA. Aiello et al. (2019), enfatizan el papel de las prácticas de gestión meritocrática en el fortalecimiento de los vínculos universidad-empresa, destacando la importancia de una gestión efectiva en la CUI. Las prácticas de gestión meritocrática en el fortalecimiento de los vínculos universidad-empresa, destacando la importancia de una gestión efectiva en la CUI.</t>
-  </si>
-  <si>
     <t>Motivación</t>
   </si>
   <si>
@@ -7855,7 +7831,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7887,11 +7863,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
     </font>
   </fonts>
   <fills count="3">
@@ -8342,10 +8313,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A3C32FBF-D320-403B-B278-AC04D1A3C016}" name="Tabla5" displayName="Tabla5" ref="C2:I556" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" tableBorderDxfId="7">
-  <autoFilter ref="C2:I556" xr:uid="{A3C32FBF-D320-403B-B278-AC04D1A3C016}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:I556">
-    <sortCondition ref="E2:E556"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A3C32FBF-D320-403B-B278-AC04D1A3C016}" name="Tabla5" displayName="Tabla5" ref="C2:I553" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" tableBorderDxfId="7">
+  <autoFilter ref="C2:I553" xr:uid="{A3C32FBF-D320-403B-B278-AC04D1A3C016}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:I553">
+    <sortCondition ref="E2:E553"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{0EC9EE99-7253-4FBD-9CD7-AA69C9636F6A}" name="ID.E" dataDxfId="6"/>
@@ -8806,49 +8777,49 @@
   <threadedComment ref="E345" dT="2026-02-22T18:33:15.66" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{1F3D1016-35CB-4496-B9BB-2F789FD603BA}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="E372" dT="2026-02-22T19:45:55.74" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{361E5AC9-792E-4D88-9E30-F522BE3016C6}">
+  <threadedComment ref="E369" dT="2026-02-22T19:45:55.74" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{361E5AC9-792E-4D88-9E30-F522BE3016C6}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="E373" dT="2026-02-22T19:45:55.74" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{FA5774CF-DDEF-4D00-818C-1C6BA1914343}">
+  <threadedComment ref="E370" dT="2026-02-22T19:45:55.74" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{FA5774CF-DDEF-4D00-818C-1C6BA1914343}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="E374" dT="2026-02-22T19:45:55.74" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{1C9A6531-14E2-43E1-A415-9922C3A9DA1C}">
+  <threadedComment ref="E371" dT="2026-02-22T19:45:55.74" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{1C9A6531-14E2-43E1-A415-9922C3A9DA1C}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="E386" dT="2026-02-22T19:52:47.56" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{B8E65C02-E5F0-437B-BA57-C86D4531CEBD}">
+  <threadedComment ref="E383" dT="2026-02-22T19:52:47.56" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{B8E65C02-E5F0-437B-BA57-C86D4531CEBD}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="E387" dT="2026-02-22T19:53:18.19" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{64839722-2100-496D-B29F-FF569669A4C7}">
+  <threadedComment ref="E384" dT="2026-02-22T19:53:18.19" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{64839722-2100-496D-B29F-FF569669A4C7}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="E391" dT="2026-02-22T19:54:41.50" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{F2DA0235-30F6-4246-A4EE-B32CF803333B}">
+  <threadedComment ref="E388" dT="2026-02-22T19:54:41.50" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{F2DA0235-30F6-4246-A4EE-B32CF803333B}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="D394" dT="2025-11-26T22:27:21.74" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{A3F8D0A1-2896-44F3-98D4-FFC3D1FEDB3B}">
+  <threadedComment ref="D391" dT="2025-11-26T22:27:21.74" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{A3F8D0A1-2896-44F3-98D4-FFC3D1FEDB3B}">
     <text>bARRERA</text>
   </threadedComment>
-  <threadedComment ref="E395" dT="2026-02-22T19:56:28.42" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{892757C9-6B28-427F-A237-1C67F9F5A22E}">
+  <threadedComment ref="E392" dT="2026-02-22T19:56:28.42" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{892757C9-6B28-427F-A237-1C67F9F5A22E}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="E428" dT="2026-02-22T20:06:43.60" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{37736932-EE25-4985-9F3C-5296BFE6712C}">
+  <threadedComment ref="E425" dT="2026-02-22T20:06:43.60" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{37736932-EE25-4985-9F3C-5296BFE6712C}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="E430" dT="2026-02-22T20:08:20.72" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{C4595140-A80D-4537-B5D0-2F070260A2E2}">
+  <threadedComment ref="E427" dT="2026-02-22T20:08:20.72" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{C4595140-A80D-4537-B5D0-2F070260A2E2}">
     <text>BARRERA</text>
   </threadedComment>
-  <threadedComment ref="E431" dT="2026-02-22T20:08:58.95" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{E31F43AA-26B0-425C-8DB9-2B88EEAA07A2}">
+  <threadedComment ref="E428" dT="2026-02-22T20:08:58.95" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{E31F43AA-26B0-425C-8DB9-2B88EEAA07A2}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="E440" dT="2026-02-22T20:13:32.46" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{53546CAF-F21F-4EEE-B5BA-BE3A63E66220}">
+  <threadedComment ref="E437" dT="2026-02-22T20:13:32.46" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{53546CAF-F21F-4EEE-B5BA-BE3A63E66220}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="E447" dT="2026-02-22T20:24:38.04" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{68A2B69D-EF21-4A73-A254-944BC17354BD}">
+  <threadedComment ref="E444" dT="2026-02-22T20:24:38.04" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{68A2B69D-EF21-4A73-A254-944BC17354BD}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="D451" dT="2025-11-26T22:25:56.57" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{9E3CDE71-45AD-4843-BF33-AC331DAC95BA}">
+  <threadedComment ref="D448" dT="2025-11-26T22:25:56.57" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{9E3CDE71-45AD-4843-BF33-AC331DAC95BA}">
     <text>Barrera</text>
   </threadedComment>
-  <threadedComment ref="D484" dT="2025-03-27T01:09:15.50" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{987AFB11-BA69-415B-B7D3-8CD963274F50}">
+  <threadedComment ref="D481" dT="2025-03-27T01:09:15.50" personId="{45DDCFB1-337E-4734-B3FB-5256CA8DF9DF}" id="{987AFB11-BA69-415B-B7D3-8CD963274F50}">
     <text>El articulo 14. Lo describe como un obstaculo</text>
   </threadedComment>
 </ThreadedComments>
@@ -8856,7 +8827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52683A34-242F-4D83-831A-DE8C357E961A}">
-  <dimension ref="B2:I556"/>
+  <dimension ref="B2:I553"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.77734375" customWidth="1"/>
@@ -8872,19 +8843,19 @@
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="13"/>
       <c r="C2" s="6" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>1</v>
@@ -8973,7 +8944,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>8</v>
@@ -9111,7 +9082,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>36</v>
@@ -9123,7 +9094,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <v>11</v>
       </c>
@@ -9180,7 +9151,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>22</v>
@@ -9291,7 +9262,7 @@
         <v>45</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>46</v>
@@ -9314,7 +9285,7 @@
         <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>48</v>
@@ -9337,7 +9308,7 @@
         <v>45</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>50</v>
@@ -9399,7 +9370,7 @@
         <v>55</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
@@ -9420,7 +9391,7 @@
         <v>58</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1" t="s">
@@ -9441,7 +9412,7 @@
         <v>60</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
@@ -9462,7 +9433,7 @@
         <v>62</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
@@ -9483,7 +9454,7 @@
         <v>64</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
@@ -9504,7 +9475,7 @@
         <v>66</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
@@ -9525,7 +9496,7 @@
         <v>56</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1" t="s">
@@ -9549,7 +9520,7 @@
         <v>70</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>71</v>
@@ -9614,7 +9585,7 @@
         <v>75</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>77</v>
@@ -9637,7 +9608,7 @@
         <v>75</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>79</v>
@@ -9660,7 +9631,7 @@
         <v>75</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>81</v>
@@ -9729,7 +9700,7 @@
         <v>75</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>87</v>
@@ -9775,7 +9746,7 @@
         <v>75</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>91</v>
@@ -9798,7 +9769,7 @@
         <v>75</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>93</v>
@@ -9888,7 +9859,7 @@
         <v>75</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>101</v>
@@ -9934,7 +9905,7 @@
         <v>75</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>105</v>
@@ -9957,10 +9928,10 @@
         <v>75</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>6</v>
@@ -9980,10 +9951,10 @@
         <v>75</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>6</v>
@@ -10006,7 +9977,7 @@
         <v>94</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>6</v>
@@ -10070,7 +10041,7 @@
         <v>75</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>113</v>
@@ -10096,7 +10067,7 @@
         <v>121</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>6</v>
@@ -10160,7 +10131,7 @@
         <v>75</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>120</v>
@@ -10206,7 +10177,7 @@
         <v>75</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>101</v>
@@ -10532,7 +10503,7 @@
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>6</v>
@@ -10573,7 +10544,7 @@
         <v>152</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>162</v>
@@ -10596,7 +10567,7 @@
         <v>152</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>164</v>
@@ -10616,10 +10587,10 @@
         <v>165</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>166</v>
@@ -10639,10 +10610,10 @@
         <v>167</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>168</v>
@@ -10662,10 +10633,10 @@
         <v>169</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>170</v>
@@ -10685,7 +10656,7 @@
         <v>171</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
@@ -10706,10 +10677,10 @@
         <v>173</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>174</v>
@@ -10729,10 +10700,10 @@
         <v>175</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>176</v>
@@ -10965,7 +10936,7 @@
         <v>178</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>196</v>
@@ -11030,7 +11001,7 @@
         <v>178</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>201</v>
@@ -11042,7 +11013,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C100" s="3">
         <v>98</v>
       </c>
@@ -11141,7 +11112,7 @@
         <v>207</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>208</v>
@@ -11164,7 +11135,7 @@
         <v>207</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>210</v>
@@ -11229,7 +11200,7 @@
         <v>207</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>215</v>
@@ -11273,7 +11244,7 @@
         <v>207</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>219</v>
@@ -11296,7 +11267,7 @@
         <v>207</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>221</v>
@@ -11308,7 +11279,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C112" s="3">
         <v>110</v>
       </c>
@@ -11319,7 +11290,7 @@
         <v>223</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>224</v>
@@ -11342,7 +11313,7 @@
         <v>223</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>226</v>
@@ -11386,7 +11357,7 @@
         <v>223</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>229</v>
@@ -11409,7 +11380,7 @@
         <v>223</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>231</v>
@@ -11432,7 +11403,7 @@
         <v>223</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>233</v>
@@ -11476,7 +11447,7 @@
         <v>223</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>237</v>
@@ -11499,7 +11470,7 @@
         <v>223</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>239</v>
@@ -11543,7 +11514,7 @@
         <v>223</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="3" t="s">
@@ -11564,7 +11535,7 @@
         <v>223</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>244</v>
@@ -11587,7 +11558,7 @@
         <v>223</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>246</v>
@@ -11631,7 +11602,7 @@
         <v>223</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>248</v>
@@ -11675,7 +11646,7 @@
         <v>252</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>253</v>
@@ -11698,7 +11669,7 @@
         <v>252</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>255</v>
@@ -11742,7 +11713,7 @@
         <v>252</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>258</v>
@@ -11807,7 +11778,7 @@
         <v>252</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>262</v>
@@ -11830,7 +11801,7 @@
         <v>252</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>264</v>
@@ -11853,10 +11824,10 @@
         <v>252</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>6</v>
@@ -11912,16 +11883,16 @@
         <v>137</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>252</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1173</v>
+        <v>1166</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="H139" s="3" t="s">
         <v>6</v>
@@ -11941,7 +11912,7 @@
         <v>275</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>276</v>
@@ -11964,7 +11935,7 @@
         <v>275</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>278</v>
@@ -11987,7 +11958,7 @@
         <v>275</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>280</v>
@@ -12010,7 +11981,7 @@
         <v>275</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>282</v>
@@ -12033,7 +12004,7 @@
         <v>275</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>284</v>
@@ -12056,7 +12027,7 @@
         <v>275</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>286</v>
@@ -12100,7 +12071,7 @@
         <v>275</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>290</v>
@@ -12123,7 +12094,7 @@
         <v>275</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>292</v>
@@ -12146,7 +12117,7 @@
         <v>275</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>294</v>
@@ -12169,7 +12140,7 @@
         <v>275</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>296</v>
@@ -12192,7 +12163,7 @@
         <v>275</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>298</v>
@@ -12236,7 +12207,7 @@
         <v>275</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>302</v>
@@ -12292,7 +12263,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="156" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C156" s="9">
         <v>154</v>
       </c>
@@ -12303,7 +12274,7 @@
         <v>304</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1098</v>
+        <v>1091</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>305</v>
@@ -12326,7 +12297,7 @@
         <v>304</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>306</v>
@@ -12370,7 +12341,7 @@
         <v>304</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1098</v>
+        <v>1091</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>310</v>
@@ -12393,7 +12364,7 @@
         <v>304</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>312</v>
@@ -12479,7 +12450,7 @@
         <v>304</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>316</v>
@@ -12502,7 +12473,7 @@
         <v>304</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>317</v>
@@ -12525,7 +12496,7 @@
         <v>304</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>319</v>
@@ -12548,7 +12519,7 @@
         <v>304</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>321</v>
@@ -12571,7 +12542,7 @@
         <v>323</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>324</v>
@@ -12594,7 +12565,7 @@
         <v>323</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>326</v>
@@ -12617,7 +12588,7 @@
         <v>323</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>328</v>
@@ -12640,7 +12611,7 @@
         <v>323</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>330</v>
@@ -12663,7 +12634,7 @@
         <v>323</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>332</v>
@@ -12686,7 +12657,7 @@
         <v>323</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>334</v>
@@ -12730,7 +12701,7 @@
         <v>323</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>338</v>
@@ -12753,7 +12724,7 @@
         <v>323</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>340</v>
@@ -12797,7 +12768,7 @@
         <v>323</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>343</v>
@@ -12820,7 +12791,7 @@
         <v>323</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>345</v>
@@ -12843,7 +12814,7 @@
         <v>323</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>347</v>
@@ -12866,7 +12837,7 @@
         <v>323</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>347</v>
@@ -12910,7 +12881,7 @@
         <v>323</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>352</v>
@@ -12954,7 +12925,7 @@
         <v>323</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>356</v>
@@ -12977,7 +12948,7 @@
         <v>323</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>357</v>
@@ -13000,10 +12971,10 @@
         <v>323</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>6</v>
@@ -13023,10 +12994,10 @@
         <v>323</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>6</v>
@@ -13046,10 +13017,10 @@
         <v>323</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>6</v>
@@ -13090,7 +13061,7 @@
         <v>323</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>364</v>
@@ -13113,7 +13084,7 @@
         <v>323</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>366</v>
@@ -13136,7 +13107,7 @@
         <v>323</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>368</v>
@@ -13159,7 +13130,7 @@
         <v>323</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>370</v>
@@ -13182,7 +13153,7 @@
         <v>323</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>372</v>
@@ -13226,7 +13197,7 @@
         <v>377</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>378</v>
@@ -13312,7 +13283,7 @@
         <v>377</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>383</v>
@@ -13356,7 +13327,7 @@
         <v>377</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>387</v>
@@ -13379,7 +13350,7 @@
         <v>377</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>389</v>
@@ -13402,7 +13373,7 @@
         <v>377</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>390</v>
@@ -13446,7 +13417,7 @@
         <v>377</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>394</v>
@@ -13469,10 +13440,10 @@
         <v>377</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
       <c r="H208" s="3" t="s">
         <v>6</v>
@@ -13492,10 +13463,10 @@
         <v>377</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>1113</v>
+        <v>1106</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>6</v>
@@ -13620,7 +13591,7 @@
         <v>377</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>404</v>
@@ -13758,7 +13729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="222" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="222" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C222" s="9">
         <v>220</v>
       </c>
@@ -13769,7 +13740,7 @@
         <v>414</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>419</v>
@@ -13813,7 +13784,7 @@
         <v>414</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>423</v>
@@ -13857,7 +13828,7 @@
         <v>463</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>464</v>
@@ -13880,7 +13851,7 @@
         <v>463</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1117</v>
+        <v>1110</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>466</v>
@@ -13924,7 +13895,7 @@
         <v>463</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>467</v>
@@ -13947,7 +13918,7 @@
         <v>463</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>469</v>
@@ -13991,10 +13962,10 @@
         <v>463</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="H232" s="3" t="s">
         <v>6</v>
@@ -14035,7 +14006,7 @@
         <v>463</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>475</v>
@@ -14079,7 +14050,7 @@
         <v>463</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>477</v>
@@ -14102,7 +14073,7 @@
         <v>463</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>479</v>
@@ -14125,7 +14096,7 @@
         <v>463</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>481</v>
@@ -14169,7 +14140,7 @@
         <v>463</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>484</v>
@@ -14213,7 +14184,7 @@
         <v>463</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>487</v>
@@ -14236,7 +14207,7 @@
         <v>463</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>489</v>
@@ -14295,14 +14266,14 @@
         <v>244</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="E246" s="10" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="F246" s="1"/>
       <c r="G246" s="1" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="H246" s="3" t="s">
         <v>6</v>
@@ -14316,16 +14287,16 @@
         <v>245</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>1212</v>
+        <v>1205</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="H247" s="3" t="s">
         <v>6</v>
@@ -14339,16 +14310,16 @@
         <v>246</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="E248" s="10" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="H248" s="3" t="s">
         <v>6</v>
@@ -14362,16 +14333,16 @@
         <v>247</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="H249" s="3" t="s">
         <v>6</v>
@@ -14388,7 +14359,7 @@
         <v>269</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="F250" s="1"/>
       <c r="G250" s="1" t="s">
@@ -14409,7 +14380,7 @@
         <v>271</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="F251" s="1"/>
       <c r="G251" s="1" t="s">
@@ -14454,7 +14425,7 @@
         <v>495</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>498</v>
@@ -14498,7 +14469,7 @@
         <v>495</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>502</v>
@@ -14521,7 +14492,7 @@
         <v>495</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>504</v>
@@ -14544,7 +14515,7 @@
         <v>510</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>511</v>
@@ -14567,7 +14538,7 @@
         <v>510</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>513</v>
@@ -14590,7 +14561,7 @@
         <v>510</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>515</v>
@@ -14613,7 +14584,7 @@
         <v>510</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>517</v>
@@ -14636,7 +14607,7 @@
         <v>510</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>519</v>
@@ -14728,7 +14699,7 @@
         <v>528</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>529</v>
@@ -14751,10 +14722,10 @@
         <v>528</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1125</v>
+        <v>1118</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1126</v>
+        <v>1119</v>
       </c>
       <c r="H266" s="3" t="s">
         <v>6</v>
@@ -14774,7 +14745,7 @@
         <v>528</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1125</v>
+        <v>1118</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>532</v>
@@ -14797,7 +14768,7 @@
         <v>528</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>1127</v>
+        <v>1120</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>534</v>
@@ -14820,7 +14791,7 @@
         <v>528</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>536</v>
@@ -14843,7 +14814,7 @@
         <v>528</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>538</v>
@@ -14935,10 +14906,10 @@
         <v>528</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
       <c r="H274" s="3" t="s">
         <v>6</v>
@@ -14981,7 +14952,7 @@
         <v>547</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>551</v>
@@ -15043,7 +15014,7 @@
         <v>556</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>559</v>
@@ -15066,7 +15037,7 @@
         <v>559</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>559</v>
@@ -15089,10 +15060,10 @@
         <v>561</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>562</v>
@@ -15112,13 +15083,13 @@
         <v>563</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>6</v>
@@ -15135,10 +15106,10 @@
         <v>564</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>565</v>
@@ -15158,7 +15129,7 @@
         <v>566</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="F284" s="1"/>
       <c r="G284" s="1" t="s">
@@ -15179,10 +15150,10 @@
         <v>568</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>569</v>
@@ -15202,10 +15173,10 @@
         <v>570</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>571</v>
@@ -15225,7 +15196,7 @@
         <v>557</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="F287" s="1"/>
       <c r="G287" s="1" t="s">
@@ -15246,10 +15217,10 @@
         <v>573</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>574</v>
@@ -15269,10 +15240,10 @@
         <v>575</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>576</v>
@@ -15292,10 +15263,10 @@
         <v>577</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>578</v>
@@ -15315,10 +15286,10 @@
         <v>579</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>580</v>
@@ -15338,10 +15309,10 @@
         <v>581</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>582</v>
@@ -15361,7 +15332,7 @@
         <v>583</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>169</v>
@@ -15384,10 +15355,10 @@
         <v>585</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>586</v>
@@ -15407,10 +15378,10 @@
         <v>587</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>588</v>
@@ -15430,10 +15401,10 @@
         <v>589</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>590</v>
@@ -15453,10 +15424,10 @@
         <v>591</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>592</v>
@@ -15476,10 +15447,10 @@
         <v>593</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>594</v>
@@ -15499,10 +15470,10 @@
         <v>595</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>596</v>
@@ -15522,10 +15493,10 @@
         <v>573</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>597</v>
@@ -15545,10 +15516,10 @@
         <v>598</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G301" s="1" t="s">
         <v>599</v>
@@ -15568,7 +15539,7 @@
         <v>600</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F302" s="1"/>
       <c r="G302" s="1" t="s">
@@ -15589,10 +15560,10 @@
         <v>602</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>603</v>
@@ -15612,10 +15583,10 @@
         <v>604</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>605</v>
@@ -15635,10 +15606,10 @@
         <v>583</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>606</v>
@@ -15658,10 +15629,10 @@
         <v>607</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>608</v>
@@ -15681,10 +15652,10 @@
         <v>611</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>612</v>
@@ -15704,10 +15675,10 @@
         <v>613</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>614</v>
@@ -15727,10 +15698,10 @@
         <v>615</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>616</v>
@@ -15750,10 +15721,10 @@
         <v>617</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>618</v>
@@ -15773,10 +15744,10 @@
         <v>619</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>620</v>
@@ -15796,10 +15767,10 @@
         <v>621</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>616</v>
@@ -15819,7 +15790,7 @@
         <v>583</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F313" s="1"/>
       <c r="G313" s="1" t="s">
@@ -15840,7 +15811,7 @@
         <v>624</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F314" s="1"/>
       <c r="G314" s="1" t="s">
@@ -15861,7 +15832,7 @@
         <v>426</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>439</v>
@@ -15884,7 +15855,7 @@
         <v>453</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>454</v>
@@ -15907,7 +15878,7 @@
         <v>439</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>439</v>
@@ -15930,7 +15901,7 @@
         <v>428</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>428</v>
@@ -15945,7 +15916,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="319" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="319" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C319" s="3">
         <v>317</v>
       </c>
@@ -15953,7 +15924,7 @@
         <v>442</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>439</v>
@@ -15976,7 +15947,7 @@
         <v>444</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>439</v>
@@ -15999,7 +15970,7 @@
         <v>430</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F321" s="1"/>
       <c r="G321" s="1" t="s">
@@ -16020,7 +15991,7 @@
         <v>432</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>432</v>
@@ -16043,7 +16014,7 @@
         <v>434</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>439</v>
@@ -16066,7 +16037,7 @@
         <v>449</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>450</v>
@@ -16089,7 +16060,7 @@
         <v>434</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F325" s="1"/>
       <c r="G325" s="1" t="s">
@@ -16110,7 +16081,7 @@
         <v>438</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>439</v>
@@ -16133,7 +16104,7 @@
         <v>447</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>439</v>
@@ -16156,7 +16127,7 @@
         <v>456</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>454</v>
@@ -16179,7 +16150,7 @@
         <v>436</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F329" s="1"/>
       <c r="G329" s="1" t="s">
@@ -16200,7 +16171,7 @@
         <v>449</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>450</v>
@@ -16223,7 +16194,7 @@
         <v>454</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>454</v>
@@ -16246,7 +16217,7 @@
         <v>459</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>454</v>
@@ -16272,7 +16243,7 @@
         <v>628</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>629</v>
@@ -16295,7 +16266,7 @@
         <v>628</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>631</v>
@@ -16341,7 +16312,7 @@
         <v>628</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>635</v>
@@ -16410,7 +16381,7 @@
         <v>628</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>472</v>
@@ -16433,7 +16404,7 @@
         <v>628</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>642</v>
@@ -16456,7 +16427,7 @@
         <v>628</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>644</v>
@@ -16502,7 +16473,7 @@
         <v>628</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>648</v>
@@ -16525,7 +16496,7 @@
         <v>628</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>650</v>
@@ -16548,7 +16519,7 @@
         <v>628</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>652</v>
@@ -16594,7 +16565,7 @@
         <v>628</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>656</v>
@@ -16611,16 +16582,16 @@
         <v>346</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>628</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>1214</v>
+        <v>1207</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="H348" s="3" t="s">
         <v>6</v>
@@ -16634,16 +16605,16 @@
         <v>347</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>628</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>1214</v>
+        <v>1207</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="H349" s="3" t="s">
         <v>6</v>
@@ -16657,16 +16628,16 @@
         <v>348</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>628</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>1214</v>
+        <v>1207</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="H350" s="3" t="s">
         <v>6</v>
@@ -16675,7 +16646,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="351" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="351" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C351" s="9">
         <v>349</v>
       </c>
@@ -16683,82 +16654,86 @@
         <v>657</v>
       </c>
       <c r="E351" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F351" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="G351" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="F351" s="1"/>
-      <c r="G351" s="1" t="s">
-        <v>659</v>
-      </c>
       <c r="H351" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I351" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="352" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="352" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C352" s="3">
         <v>350</v>
       </c>
       <c r="D352" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F352" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="G352" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="E352" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="F352" s="1"/>
-      <c r="G352" s="1" t="s">
-        <v>661</v>
-      </c>
       <c r="H352" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I352" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="353" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="353" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C353" s="3">
         <v>351</v>
       </c>
       <c r="D353" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F353" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="G353" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="E353" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="F353" s="1"/>
-      <c r="G353" s="1" t="s">
-        <v>663</v>
-      </c>
       <c r="H353" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I353" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="354" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="354" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C354" s="9">
         <v>352</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F354" s="1" t="s">
-        <v>666</v>
-      </c>
+        <v>657</v>
+      </c>
+      <c r="F354" s="1"/>
       <c r="G354" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H354" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I354" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="355" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -16766,112 +16741,114 @@
         <v>353</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="E355" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F355" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G355" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="F355" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="G355" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="H355" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I355" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="356" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="356" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C356" s="3">
         <v>354</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="H356" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I356" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="357" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="357" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C357" s="9">
         <v>355</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F357" s="1"/>
+        <v>657</v>
+      </c>
+      <c r="F357" s="1" t="s">
+        <v>1141</v>
+      </c>
       <c r="G357" s="1" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H357" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I357" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="358" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="358" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C358" s="3">
         <v>356</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="H358" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I358" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="359" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="359" spans="3:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="C359" s="3">
         <v>357</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>666</v>
+        <v>1141</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H359" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I359" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="360" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
@@ -16879,365 +16856,365 @@
         <v>358</v>
       </c>
       <c r="D360" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="E360" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F360" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G360" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="E360" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F360" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="G360" s="1" t="s">
-        <v>674</v>
-      </c>
       <c r="H360" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I360" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="361" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="361" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C361" s="3">
         <v>359</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>676</v>
+        <v>1143</v>
       </c>
       <c r="H361" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I361" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="362" spans="3:9" ht="187.2" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="362" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C362" s="3">
         <v>360</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H362" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I362" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="363" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="363" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C363" s="9">
         <v>361</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="H363" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I363" s="3">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="364" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="364" spans="3:9" ht="144" x14ac:dyDescent="0.3">
       <c r="C364" s="3">
         <v>362</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>1150</v>
+        <v>679</v>
       </c>
       <c r="H364" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I364" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="365" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="365" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C365" s="3">
         <v>363</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H365" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I365" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="366" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="366" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C366" s="9">
         <v>364</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F366" s="1" t="s">
-        <v>1151</v>
-      </c>
+        <v>657</v>
+      </c>
+      <c r="F366" s="1"/>
       <c r="G366" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H366" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I366" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="367" spans="3:9" ht="144" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="367" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C367" s="3">
         <v>365</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H367" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I367" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="368" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="368" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C368" s="3">
         <v>366</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>1152</v>
+        <v>1142</v>
       </c>
       <c r="G368" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H368" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I368" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="369" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="369" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C369" s="9">
         <v>367</v>
       </c>
       <c r="D369" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="E369" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="E369" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F369" s="1"/>
+      <c r="F369" s="1" t="s">
+        <v>1146</v>
+      </c>
       <c r="G369" s="1" t="s">
-        <v>689</v>
+        <v>1147</v>
       </c>
       <c r="H369" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I369" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="370" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="370" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C370" s="3">
         <v>368</v>
       </c>
       <c r="D370" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="E370" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F370" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G370" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="E370" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F370" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="G370" s="1" t="s">
-        <v>691</v>
-      </c>
       <c r="H370" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I370" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="371" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="371" spans="3:9" ht="144" x14ac:dyDescent="0.3">
       <c r="C371" s="3">
         <v>369</v>
       </c>
       <c r="D371" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E371" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F371" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G371" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="E371" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F371" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="G371" s="1" t="s">
-        <v>693</v>
-      </c>
       <c r="H371" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I371" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="372" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="372" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C372" s="9">
         <v>370</v>
       </c>
       <c r="D372" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E372" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F372" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G372" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="E372" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F372" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G372" s="1" t="s">
-        <v>1154</v>
-      </c>
       <c r="H372" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I372" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="373" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="373" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C373" s="3">
         <v>371</v>
       </c>
       <c r="D373" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="E373" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F373" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G373" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="E373" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F373" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G373" s="1" t="s">
-        <v>697</v>
-      </c>
       <c r="H373" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I373" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="374" spans="3:9" ht="144" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="374" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C374" s="3">
         <v>372</v>
       </c>
       <c r="D374" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="E374" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F374" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G374" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="E374" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F374" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G374" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="H374" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I374" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="375" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="375" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C375" s="9">
         <v>373</v>
       </c>
       <c r="D375" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="E375" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F375" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G375" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="E375" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F375" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G375" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="H375" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I375" s="3">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="376" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -17245,229 +17222,225 @@
         <v>374</v>
       </c>
       <c r="D376" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="E376" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F376" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G376" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="E376" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F376" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G376" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="H376" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I376" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="377" spans="3:9" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="377" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C377" s="3">
         <v>375</v>
       </c>
       <c r="D377" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="E377" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F377" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G377" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="E377" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F377" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G377" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="H377" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I377" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="378" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="378" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C378" s="9">
         <v>376</v>
       </c>
       <c r="D378" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="E378" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F378" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G378" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="E378" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F378" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="G378" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="H378" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I378" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="379" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="379" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C379" s="3">
         <v>377</v>
       </c>
       <c r="D379" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="E379" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F379" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G379" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="E379" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F379" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G379" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="H379" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I379" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="380" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="380" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C380" s="3">
         <v>378</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>710</v>
+        <v>812</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>1157</v>
+        <v>1178</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>711</v>
+        <v>813</v>
       </c>
       <c r="H380" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I380" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="381" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="381" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C381" s="9">
         <v>379</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>712</v>
+        <v>814</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>1157</v>
+        <v>1179</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>713</v>
+        <v>815</v>
       </c>
       <c r="H381" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I381" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="382" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="382" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C382" s="3">
         <v>380</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>695</v>
+        <v>710</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="H382" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I382" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="383" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="383" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C383" s="3">
         <v>381</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>819</v>
+        <v>712</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F383" s="1" t="s">
-        <v>1185</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="F383" s="1"/>
       <c r="G383" s="1" t="s">
-        <v>820</v>
+        <v>713</v>
       </c>
       <c r="H383" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I383" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="384" spans="3:9" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="384" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C384" s="9">
         <v>382</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>821</v>
+        <v>714</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F384" s="1" t="s">
-        <v>1186</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="F384" s="1"/>
       <c r="G384" s="1" t="s">
-        <v>822</v>
+        <v>715</v>
       </c>
       <c r="H384" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I384" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="385" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="385" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C385" s="3">
         <v>383</v>
       </c>
       <c r="D385" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E385" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="F385" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G385" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="E385" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="F385" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="G385" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="H385" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I385" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="386" spans="3:9" ht="72" x14ac:dyDescent="0.3">
@@ -17475,131 +17448,135 @@
         <v>384</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="E386" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="F386" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G386" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="F386" s="1"/>
-      <c r="G386" s="1" t="s">
-        <v>720</v>
-      </c>
       <c r="H386" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I386" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="387" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="387" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C387" s="9">
         <v>385</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="F387" s="1"/>
+        <v>710</v>
+      </c>
+      <c r="F387" s="1" t="s">
+        <v>1153</v>
+      </c>
       <c r="G387" s="1" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="H387" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I387" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="388" spans="3:9" ht="144" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="388" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C388" s="3">
         <v>386</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="F388" s="1" t="s">
-        <v>1159</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="F388" s="1"/>
       <c r="G388" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="H388" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I388" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="389" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="389" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C389" s="3">
         <v>387</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1160</v>
+        <v>1151</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H389" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I389" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="390" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="390" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C390" s="9">
         <v>388</v>
       </c>
       <c r="D390" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E390" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="F390" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G390" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="E390" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="F390" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="G390" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="H390" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I390" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="391" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="391" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C391" s="3">
         <v>389</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="F391" s="1"/>
+        <v>710</v>
+      </c>
+      <c r="F391" s="1" t="s">
+        <v>1151</v>
+      </c>
       <c r="G391" s="1" t="s">
-        <v>728</v>
+        <v>1155</v>
       </c>
       <c r="H391" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I391" s="3">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="392" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
@@ -17607,22 +17584,20 @@
         <v>390</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="F392" s="1" t="s">
-        <v>1158</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="F392" s="1"/>
       <c r="G392" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="H392" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I392" s="3">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="393" spans="3:9" ht="72" x14ac:dyDescent="0.3">
@@ -17630,69 +17605,69 @@
         <v>391</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1161</v>
+        <v>1151</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="H393" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I393" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="394" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="394" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C394" s="3">
         <v>392</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>1162</v>
+        <v>732</v>
       </c>
       <c r="H394" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I394" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="395" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="395" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C395" s="3">
         <v>393</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="F395" s="1"/>
       <c r="G395" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="H395" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I395" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="H395" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I395" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="396" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="396" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C396" s="9">
         <v>394</v>
       </c>
@@ -17700,84 +17675,86 @@
         <v>736</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="F396" s="1" t="s">
-        <v>1158</v>
-      </c>
+        <v>737</v>
+      </c>
+      <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H396" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I396" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="397" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C397" s="3">
         <v>395</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H397" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I397" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="398" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="398" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C398" s="3">
         <v>396</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="F398" s="1"/>
+        <v>737</v>
+      </c>
+      <c r="F398" s="1" t="s">
+        <v>1157</v>
+      </c>
       <c r="G398" s="1" t="s">
-        <v>741</v>
+        <v>1158</v>
       </c>
       <c r="H398" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I398" s="3" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="399" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="I398" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="399" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C399" s="9">
         <v>397</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="F399" s="1"/>
+        <v>737</v>
+      </c>
+      <c r="F399" s="1" t="s">
+        <v>1156</v>
+      </c>
       <c r="G399" s="1" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="H399" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I399" s="3">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="400" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -17785,205 +17762,205 @@
         <v>398</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="E400" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="F400" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G400" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="F400" s="1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="G400" s="1" t="s">
-        <v>747</v>
-      </c>
       <c r="H400" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I400" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="401" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="401" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C401" s="3">
         <v>399</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="G401" s="1" t="s">
-        <v>1165</v>
+        <v>746</v>
       </c>
       <c r="H401" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I401" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="402" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="402" spans="3:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="C402" s="9">
         <v>400</v>
       </c>
       <c r="D402" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="E402" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="F402" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G402" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="E402" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="F402" s="1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="G402" s="1" t="s">
-        <v>749</v>
-      </c>
       <c r="H402" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I402" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="403" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="403" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C403" s="3">
         <v>401</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="G403" s="1" t="s">
-        <v>751</v>
+        <v>1162</v>
       </c>
       <c r="H403" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I403" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="404" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="404" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C404" s="3">
         <v>402</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="F404" s="1" t="s">
-        <v>1167</v>
-      </c>
+        <v>737</v>
+      </c>
+      <c r="F404" s="1"/>
       <c r="G404" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="H404" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I404" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="405" spans="3:9" ht="158.4" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="405" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C405" s="9">
         <v>403</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="F405" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="F405" s="1"/>
+      <c r="G405" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="G405" s="1" t="s">
-        <v>755</v>
-      </c>
       <c r="H405" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I405" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="406" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="406" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C406" s="3">
         <v>404</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>1168</v>
+        <v>1156</v>
       </c>
       <c r="G406" s="1" t="s">
-        <v>1169</v>
+        <v>754</v>
       </c>
       <c r="H406" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I406" s="3">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="407" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="407" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C407" s="3">
         <v>405</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="F407" s="1"/>
+        <v>737</v>
+      </c>
+      <c r="F407" s="1" t="s">
+        <v>1164</v>
+      </c>
       <c r="G407" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="H407" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I407" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="408" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="408" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C408" s="9">
         <v>406</v>
       </c>
       <c r="D408" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="E408" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="F408" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="G408" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="E408" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="F408" s="1"/>
-      <c r="G408" s="1" t="s">
-        <v>1170</v>
-      </c>
       <c r="H408" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I408" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="409" spans="3:9" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="409" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C409" s="3">
         <v>407</v>
       </c>
@@ -17991,10 +17968,10 @@
         <v>760</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>744</v>
+        <v>758</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>761</v>
@@ -18003,7 +17980,7 @@
         <v>6</v>
       </c>
       <c r="I409" s="3">
-        <v>61</v>
+        <v>8</v>
       </c>
     </row>
     <row r="410" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -18011,59 +17988,59 @@
         <v>408</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>744</v>
+        <v>758</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="G410" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="H410" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I410" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="411" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="411" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C411" s="9">
         <v>409</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="G411" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H411" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I411" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="412" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="412" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C412" s="3">
         <v>410</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>768</v>
@@ -18072,30 +18049,30 @@
         <v>6</v>
       </c>
       <c r="I412" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="413" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="413" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C413" s="3">
         <v>411</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>1174</v>
+        <v>766</v>
       </c>
       <c r="G413" s="1" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="H413" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I413" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="414" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -18103,22 +18080,22 @@
         <v>412</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="H414" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I414" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="415" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -18126,91 +18103,91 @@
         <v>413</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>1174</v>
+        <v>776</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="H415" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I415" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="416" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="416" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C416" s="3">
         <v>414</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H416" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I416" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="417" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="417" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C417" s="9">
         <v>415</v>
       </c>
       <c r="D417" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="E417" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="F417" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="G417" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="E417" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="F417" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="G417" s="1" t="s">
-        <v>778</v>
-      </c>
       <c r="H417" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I417" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="418" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="418" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C418" s="3">
         <v>416</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>783</v>
+        <v>1167</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="H418" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I418" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="419" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -18218,39 +18195,37 @@
         <v>417</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="H419" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I419" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="420" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="420" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C420" s="9">
         <v>418</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="F420" s="1" t="s">
-        <v>783</v>
-      </c>
+        <v>758</v>
+      </c>
+      <c r="F420" s="1"/>
       <c r="G420" s="1" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="H420" s="3" t="s">
         <v>6</v>
@@ -18259,203 +18234,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="421" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="421" spans="3:9" ht="144" x14ac:dyDescent="0.3">
       <c r="C421" s="3">
         <v>419</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>771</v>
+        <v>973</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>1174</v>
+        <v>780</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>785</v>
+        <v>974</v>
       </c>
       <c r="H421" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I421" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="422" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="422" spans="3:9" ht="216" x14ac:dyDescent="0.3">
       <c r="C422" s="3">
         <v>420</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>773</v>
+        <v>155</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="F422" s="1" t="s">
-        <v>773</v>
-      </c>
+        <v>1064</v>
+      </c>
+      <c r="F422" s="1"/>
       <c r="G422" s="1" t="s">
-        <v>786</v>
+        <v>156</v>
       </c>
       <c r="H422" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I422" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="423" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="423" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C423" s="9">
         <v>421</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>787</v>
+        <v>157</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>765</v>
+        <v>1064</v>
       </c>
       <c r="F423" s="1"/>
       <c r="G423" s="1" t="s">
-        <v>788</v>
+        <v>158</v>
       </c>
       <c r="H423" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I423" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="424" spans="3:9" ht="144" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="424" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C424" s="3">
         <v>422</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>980</v>
+        <v>159</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="F424" s="1" t="s">
-        <v>787</v>
-      </c>
+        <v>1064</v>
+      </c>
+      <c r="F424" s="1"/>
       <c r="G424" s="1" t="s">
-        <v>981</v>
+        <v>160</v>
       </c>
       <c r="H424" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I424" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="425" spans="3:9" ht="216" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="425" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C425" s="3">
         <v>423</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>155</v>
+        <v>782</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="F425" s="1"/>
+        <v>783</v>
+      </c>
+      <c r="F425" s="1" t="s">
+        <v>1168</v>
+      </c>
       <c r="G425" s="1" t="s">
-        <v>156</v>
+        <v>1169</v>
       </c>
       <c r="H425" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I425" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="426" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C426" s="9">
         <v>424</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>157</v>
+        <v>784</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="F426" s="1"/>
+        <v>783</v>
+      </c>
+      <c r="F426" s="1" t="s">
+        <v>1170</v>
+      </c>
       <c r="G426" s="1" t="s">
-        <v>158</v>
+        <v>1171</v>
       </c>
       <c r="H426" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I426" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="427" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="427" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C427" s="3">
         <v>425</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>159</v>
+        <v>783</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>1071</v>
+        <v>783</v>
       </c>
       <c r="F427" s="1"/>
       <c r="G427" s="1" t="s">
-        <v>160</v>
+        <v>785</v>
       </c>
       <c r="H427" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I427" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="428" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="428" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C428" s="3">
         <v>426</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>1176</v>
+        <v>786</v>
       </c>
       <c r="H428" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I428" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="429" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="429" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C429" s="9">
         <v>427</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>1177</v>
+        <v>1170</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>1178</v>
+        <v>788</v>
       </c>
       <c r="H429" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I429" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="430" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -18463,135 +18438,135 @@
         <v>428</v>
       </c>
       <c r="D430" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="E430" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F430" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G430" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="E430" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F430" s="1"/>
-      <c r="G430" s="1" t="s">
-        <v>792</v>
-      </c>
       <c r="H430" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I430" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="431" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="431" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C431" s="3">
         <v>429</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H431" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I431" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="432" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="432" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C432" s="9">
         <v>430</v>
       </c>
       <c r="D432" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="E432" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F432" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G432" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="E432" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F432" s="1" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G432" s="1" t="s">
-        <v>795</v>
-      </c>
       <c r="H432" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I432" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="433" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="433" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C433" s="3">
         <v>431</v>
       </c>
       <c r="D433" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="E433" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F433" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G433" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="E433" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F433" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="G433" s="1" t="s">
-        <v>797</v>
-      </c>
       <c r="H433" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I433" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="434" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="434" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C434" s="3">
         <v>432</v>
       </c>
       <c r="D434" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="E434" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F434" s="1"/>
+      <c r="G434" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="E434" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F434" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="G434" s="1" t="s">
-        <v>799</v>
-      </c>
       <c r="H434" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I434" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="435" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="435" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C435" s="9">
         <v>433</v>
       </c>
       <c r="D435" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="E435" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F435" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G435" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="E435" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F435" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="G435" s="1" t="s">
-        <v>801</v>
-      </c>
       <c r="H435" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I435" s="3">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="436" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -18599,156 +18574,152 @@
         <v>434</v>
       </c>
       <c r="D436" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="E436" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F436" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G436" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="E436" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F436" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="G436" s="1" t="s">
-        <v>803</v>
-      </c>
       <c r="H436" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I436" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="437" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="437" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C437" s="3">
         <v>435</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="F437" s="1"/>
       <c r="G437" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H437" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I437" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="438" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="438" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C438" s="9">
         <v>436</v>
       </c>
       <c r="D438" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="E438" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F438" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G438" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="E438" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F438" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="G438" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="H438" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I438" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="439" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="439" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C439" s="3">
         <v>437</v>
       </c>
       <c r="D439" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="E439" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F439" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G439" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="E439" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F439" s="1" t="s">
-        <v>1175</v>
-      </c>
-      <c r="G439" s="1" t="s">
-        <v>809</v>
-      </c>
       <c r="H439" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I439" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="440" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="440" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C440" s="3">
         <v>438</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>790</v>
+        <v>809</v>
       </c>
       <c r="F440" s="1"/>
       <c r="G440" s="1" t="s">
-        <v>811</v>
+        <v>1177</v>
       </c>
       <c r="H440" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I440" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="441" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="441" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C441" s="9">
         <v>439</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F441" s="1" t="s">
-        <v>1180</v>
-      </c>
+        <v>809</v>
+      </c>
+      <c r="F441" s="1"/>
       <c r="G441" s="1" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="H441" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I441" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="442" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="442" spans="3:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="C442" s="3">
         <v>440</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F442" s="1" t="s">
-        <v>1180</v>
-      </c>
+        <v>809</v>
+      </c>
+      <c r="F442" s="1"/>
       <c r="G442" s="1" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="H442" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I442" s="3">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="443" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
@@ -18756,44 +18727,44 @@
         <v>441</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="F443" s="1"/>
       <c r="G443" s="1" t="s">
-        <v>1184</v>
+        <v>820</v>
       </c>
       <c r="H443" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I443" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="444" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="3:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="C444" s="9">
         <v>442</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="F444" s="1"/>
       <c r="G444" s="1" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="H444" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I444" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="445" spans="3:9" ht="187.2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C445" s="3">
         <v>443</v>
       </c>
@@ -18801,7 +18772,7 @@
         <v>823</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="F445" s="1"/>
       <c r="G445" s="1" t="s">
@@ -18811,10 +18782,10 @@
         <v>6</v>
       </c>
       <c r="I445" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="446" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="446" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C446" s="3">
         <v>444</v>
       </c>
@@ -18822,38 +18793,38 @@
         <v>825</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="F446" s="1"/>
       <c r="G446" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H446" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I446" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="447" spans="3:9" ht="158.4" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="447" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C447" s="9">
         <v>445</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="F447" s="1"/>
       <c r="G447" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H447" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I447" s="3">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="448" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -18861,194 +18832,194 @@
         <v>446</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="F448" s="1"/>
       <c r="G448" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H448" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I448" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="449" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="449" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C449" s="3">
         <v>447</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="F449" s="1"/>
       <c r="G449" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H449" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I449" s="3">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="450" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="450" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C450" s="9">
         <v>448</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="F450" s="1"/>
+        <v>819</v>
+      </c>
+      <c r="F450" s="1" t="s">
+        <v>1181</v>
+      </c>
       <c r="G450" s="1" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="H450" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I450" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="451" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="451" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C451" s="3">
         <v>449</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="F451" s="1"/>
       <c r="G451" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H451" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I451" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="452" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="452" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C452" s="3">
         <v>450</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="F452" s="1"/>
+        <v>819</v>
+      </c>
+      <c r="F452" s="1" t="s">
+        <v>1182</v>
+      </c>
       <c r="G452" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H452" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I452" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="453" spans="3:9" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="453" spans="3:9" ht="216" x14ac:dyDescent="0.3">
       <c r="C453" s="9">
         <v>451</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>844</v>
+        <v>506</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>826</v>
+        <v>506</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H453" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I453" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="454" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="454" spans="3:9" ht="144" x14ac:dyDescent="0.3">
       <c r="C454" s="3">
         <v>452</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>846</v>
+        <v>505</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>826</v>
+        <v>506</v>
       </c>
       <c r="F454" s="1"/>
       <c r="G454" s="1" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="H454" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I454" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="455" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="455" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C455" s="3">
         <v>453</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>848</v>
+        <v>505</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="F455" s="1" t="s">
-        <v>1189</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="F455" s="1"/>
       <c r="G455" s="1" t="s">
-        <v>849</v>
+        <v>133</v>
       </c>
       <c r="H455" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I455" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="456" spans="3:9" ht="230.4" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="456" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C456" s="9">
         <v>454</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>506</v>
+        <v>845</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F456" s="1" t="s">
-        <v>1190</v>
-      </c>
+      <c r="F456" s="1"/>
       <c r="G456" s="1" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="H456" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I456" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="457" spans="3:9" ht="144" x14ac:dyDescent="0.3">
@@ -19056,171 +19027,171 @@
         <v>455</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>506</v>
       </c>
       <c r="F457" s="1"/>
       <c r="G457" s="1" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="H457" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I457" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="458" spans="3:9" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="458" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C458" s="3">
         <v>456</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>505</v>
+        <v>848</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F458" s="1"/>
+      <c r="F458" s="1" t="s">
+        <v>852</v>
+      </c>
       <c r="G458" s="1" t="s">
-        <v>133</v>
+        <v>849</v>
       </c>
       <c r="H458" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I458" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="459" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="459" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C459" s="9">
         <v>457</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>506</v>
       </c>
       <c r="F459" s="1"/>
       <c r="G459" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="H459" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I459" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="460" spans="3:9" ht="144" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="460" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C460" s="3">
         <v>458</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>506</v>
+        <v>852</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>506</v>
       </c>
       <c r="F460" s="1"/>
       <c r="G460" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H460" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I460" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="461" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="461" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C461" s="3">
         <v>459</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>855</v>
+        <v>506</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>506</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="H461" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I461" s="3">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="462" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="462" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C462" s="9">
         <v>460</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>506</v>
       </c>
       <c r="F462" s="1"/>
       <c r="G462" s="1" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="H462" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I462" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="463" spans="3:9" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="463" spans="3:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="C463" s="3">
         <v>461</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>506</v>
       </c>
       <c r="F463" s="1"/>
       <c r="G463" s="1" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="H463" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I463" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="464" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="464" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C464" s="3">
         <v>462</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>506</v>
+        <v>858</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F464" s="1" t="s">
+      <c r="F464" s="1"/>
+      <c r="G464" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="G464" s="1" t="s">
-        <v>861</v>
-      </c>
       <c r="H464" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I464" s="3">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="465" spans="3:9" x14ac:dyDescent="0.3">
@@ -19228,146 +19199,148 @@
         <v>463</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>862</v>
+        <v>845</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>506</v>
       </c>
       <c r="F465" s="1"/>
       <c r="G465" s="1" t="s">
-        <v>860</v>
+        <v>133</v>
       </c>
       <c r="H465" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I465" s="3">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="466" spans="3:9" ht="158.4" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="466" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C466" s="3">
         <v>464</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>863</v>
+        <v>852</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>506</v>
       </c>
       <c r="F466" s="1"/>
       <c r="G466" s="1" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="H466" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I466" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="467" spans="3:9" ht="129.6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="467" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C467" s="3">
         <v>465</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>506</v>
       </c>
       <c r="F467" s="1"/>
       <c r="G467" s="1" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="H467" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I467" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="468" spans="3:9" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="468" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C468" s="9">
         <v>466</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>506</v>
       </c>
       <c r="F468" s="1"/>
       <c r="G468" s="1" t="s">
-        <v>133</v>
+        <v>864</v>
       </c>
       <c r="H468" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I468" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="469" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="469" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C469" s="3">
         <v>467</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>859</v>
+        <v>876</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F469" s="1"/>
+      <c r="F469" s="1" t="s">
+        <v>1184</v>
+      </c>
       <c r="G469" s="1" t="s">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="H469" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I469" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="470" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="470" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C470" s="3">
         <v>468</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>868</v>
+        <v>835</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>506</v>
+        <v>865</v>
       </c>
       <c r="F470" s="1"/>
       <c r="G470" s="1" t="s">
-        <v>869</v>
+        <v>836</v>
       </c>
       <c r="H470" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I470" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="471" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="471" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C471" s="9">
         <v>469</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>506</v>
+        <v>865</v>
       </c>
       <c r="F471" s="1"/>
       <c r="G471" s="1" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="H471" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I471" s="3">
-        <v>62</v>
+        <v>3</v>
       </c>
     </row>
     <row r="472" spans="3:9" x14ac:dyDescent="0.3">
@@ -19375,43 +19348,41 @@
         <v>470</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>883</v>
+        <v>867</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="F472" s="1" t="s">
-        <v>1191</v>
-      </c>
+        <v>865</v>
+      </c>
+      <c r="F472" s="1"/>
       <c r="G472" s="1" t="s">
-        <v>884</v>
+        <v>133</v>
       </c>
       <c r="H472" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I472" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="473" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="473" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C473" s="3">
         <v>471</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>842</v>
+        <v>868</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="F473" s="1"/>
       <c r="G473" s="1" t="s">
-        <v>843</v>
+        <v>869</v>
       </c>
       <c r="H473" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I473" s="3">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="474" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
@@ -19419,20 +19390,20 @@
         <v>472</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F474" s="1"/>
       <c r="G474" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H474" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I474" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="475" spans="3:9" x14ac:dyDescent="0.3">
@@ -19440,10 +19411,10 @@
         <v>473</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F475" s="1"/>
       <c r="G475" s="1" t="s">
@@ -19453,94 +19424,100 @@
         <v>6</v>
       </c>
       <c r="I475" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="476" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="476" spans="3:9" ht="144" x14ac:dyDescent="0.3">
       <c r="C476" s="3">
         <v>474</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F476" s="1"/>
       <c r="G476" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H476" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I476" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="477" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="477" spans="3:9" ht="144" x14ac:dyDescent="0.3">
       <c r="C477" s="9">
         <v>475</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="F477" s="1"/>
+        <v>879</v>
+      </c>
+      <c r="F477" s="1" t="s">
+        <v>1185</v>
+      </c>
       <c r="G477" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H477" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I477" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="478" spans="3:9" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="478" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C478" s="3">
         <v>476</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="F478" s="1"/>
+        <v>879</v>
+      </c>
+      <c r="F478" s="1" t="s">
+        <v>901</v>
+      </c>
       <c r="G478" s="1" t="s">
-        <v>133</v>
+        <v>882</v>
       </c>
       <c r="H478" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I478" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="479" spans="3:9" ht="144" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="479" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C479" s="3">
         <v>477</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="F479" s="1"/>
+        <v>879</v>
+      </c>
+      <c r="F479" s="1" t="s">
+        <v>1186</v>
+      </c>
       <c r="G479" s="1" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="H479" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I479" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="480" spans="3:9" ht="144" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="480" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C480" s="9">
         <v>478</v>
       </c>
@@ -19548,65 +19525,65 @@
         <v>885</v>
       </c>
       <c r="E480" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F480" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G480" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="F480" s="1" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G480" s="1" t="s">
-        <v>887</v>
-      </c>
       <c r="H480" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I480" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="481" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="481" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C481" s="3">
         <v>479</v>
       </c>
       <c r="D481" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="E481" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F481" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G481" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="E481" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F481" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="G481" s="1" t="s">
-        <v>889</v>
-      </c>
       <c r="H481" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I481" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="482" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="482" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C482" s="3">
         <v>480</v>
       </c>
       <c r="D482" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="E482" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F482" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G482" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="E482" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F482" s="1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="G482" s="1" t="s">
-        <v>891</v>
-      </c>
       <c r="H482" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I482" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="483" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -19614,68 +19591,68 @@
         <v>481</v>
       </c>
       <c r="D483" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="E483" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F483" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G483" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="E483" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F483" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="G483" s="1" t="s">
-        <v>893</v>
-      </c>
       <c r="H483" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I483" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="484" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="484" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C484" s="3">
         <v>482</v>
       </c>
       <c r="D484" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="E484" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F484" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G484" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="E484" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F484" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="G484" s="1" t="s">
-        <v>895</v>
-      </c>
       <c r="H484" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I484" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="485" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="485" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C485" s="3">
         <v>483</v>
       </c>
       <c r="D485" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="E485" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F485" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G485" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="E485" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F485" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="G485" s="1" t="s">
-        <v>897</v>
-      </c>
       <c r="H485" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I485" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="486" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -19683,45 +19660,45 @@
         <v>484</v>
       </c>
       <c r="D486" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="E486" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F486" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G486" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="E486" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F486" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="G486" s="1" t="s">
-        <v>899</v>
-      </c>
       <c r="H486" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I486" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="487" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="487" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C487" s="3">
         <v>485</v>
       </c>
       <c r="D487" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="E487" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F487" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G487" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="E487" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F487" s="1" t="s">
-        <v>1194</v>
-      </c>
-      <c r="G487" s="1" t="s">
-        <v>901</v>
-      </c>
       <c r="H487" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I487" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="488" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -19729,177 +19706,177 @@
         <v>486</v>
       </c>
       <c r="D488" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="E488" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F488" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G488" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="E488" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F488" s="1" t="s">
-        <v>1195</v>
-      </c>
-      <c r="G488" s="1" t="s">
-        <v>903</v>
-      </c>
       <c r="H488" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I488" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="489" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="489" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C489" s="9">
         <v>487</v>
       </c>
       <c r="D489" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="E489" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F489" s="1"/>
+      <c r="G489" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="E489" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F489" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="G489" s="1" t="s">
-        <v>905</v>
-      </c>
       <c r="H489" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I489" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="490" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="490" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C490" s="3">
         <v>488</v>
       </c>
       <c r="D490" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="E490" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F490" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G490" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="E490" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F490" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="G490" s="1" t="s">
-        <v>907</v>
-      </c>
       <c r="H490" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I490" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="491" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="491" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C491" s="3">
         <v>489</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>908</v>
+        <v>879</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F491" s="1" t="s">
-        <v>908</v>
-      </c>
+        <v>879</v>
+      </c>
+      <c r="F491" s="1"/>
       <c r="G491" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="H491" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I491" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="492" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="492" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C492" s="9">
         <v>490</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="F492" s="1"/>
       <c r="G492" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="H492" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I492" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="493" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="493" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C493" s="3">
         <v>491</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>908</v>
+        <v>129</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H493" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I493" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="494" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="494" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C494" s="3">
         <v>492</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>886</v>
+        <v>912</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F494" s="1"/>
+        <v>879</v>
+      </c>
+      <c r="F494" s="1" t="s">
+        <v>934</v>
+      </c>
       <c r="G494" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H494" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I494" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="495" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="495" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C495" s="9">
         <v>493</v>
       </c>
       <c r="D495" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="E495" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F495" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G495" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="E495" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F495" s="1"/>
-      <c r="G495" s="1" t="s">
-        <v>916</v>
-      </c>
       <c r="H495" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I495" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="496" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -19907,244 +19884,242 @@
         <v>494</v>
       </c>
       <c r="D496" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="E496" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F496" s="1"/>
+      <c r="G496" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="E496" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F496" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G496" s="1" t="s">
-        <v>918</v>
-      </c>
       <c r="H496" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I496" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="497" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="497" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C497" s="3">
         <v>495</v>
       </c>
       <c r="D497" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E497" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F497" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G497" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="E497" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F497" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="G497" s="1" t="s">
-        <v>920</v>
-      </c>
       <c r="H497" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I497" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="498" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="498" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C498" s="9">
         <v>496</v>
       </c>
       <c r="D498" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="E498" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F498" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G498" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="E498" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F498" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="G498" s="1" t="s">
-        <v>922</v>
-      </c>
       <c r="H498" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I498" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="499" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="499" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C499" s="3">
         <v>497</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="F499" s="1"/>
       <c r="G499" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H499" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I499" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="500" spans="3:9" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="500" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C500" s="3">
         <v>498</v>
       </c>
       <c r="D500" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="E500" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F500" s="1"/>
+      <c r="G500" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="E500" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F500" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="G500" s="1" t="s">
-        <v>926</v>
-      </c>
       <c r="H500" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I500" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="501" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="501" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C501" s="9">
         <v>499</v>
       </c>
       <c r="D501" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="E501" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F501" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G501" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="E501" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F501" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="G501" s="1" t="s">
-        <v>928</v>
-      </c>
       <c r="H501" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I501" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="502" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="502" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C502" s="3">
         <v>500</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E502" s="1" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="F502" s="1"/>
       <c r="G502" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H502" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I502" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="503" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="503" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C503" s="3">
         <v>501</v>
       </c>
       <c r="D503" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="E503" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F503" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="G503" s="5" t="s">
         <v>931</v>
       </c>
-      <c r="E503" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F503" s="1"/>
-      <c r="G503" s="1" t="s">
-        <v>932</v>
-      </c>
       <c r="H503" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I503" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="504" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="504" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C504" s="9">
         <v>502</v>
       </c>
       <c r="D504" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="E504" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F504" s="1"/>
+      <c r="G504" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="E504" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F504" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="G504" s="1" t="s">
-        <v>934</v>
-      </c>
       <c r="H504" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I504" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="505" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="505" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C505" s="3">
         <v>503</v>
       </c>
       <c r="D505" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="E505" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F505" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="G505" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="E505" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F505" s="1"/>
-      <c r="G505" s="1" t="s">
-        <v>936</v>
-      </c>
       <c r="H505" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I505" s="3">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="506" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="506" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C506" s="3">
         <v>504</v>
       </c>
       <c r="D506" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="E506" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F506" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G506" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="E506" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F506" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="G506" s="5" t="s">
-        <v>938</v>
-      </c>
       <c r="H506" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I506" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="507" spans="3:9" ht="72" x14ac:dyDescent="0.3">
@@ -20152,66 +20127,68 @@
         <v>505</v>
       </c>
       <c r="D507" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="E507" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F507" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G507" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="E507" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F507" s="1"/>
-      <c r="G507" s="1" t="s">
-        <v>940</v>
-      </c>
       <c r="H507" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I507" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="508" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="508" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C508" s="3">
         <v>506</v>
       </c>
       <c r="D508" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="E508" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F508" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="G508" s="1" t="s">
         <v>941</v>
       </c>
-      <c r="E508" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F508" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="G508" s="1" t="s">
-        <v>942</v>
-      </c>
       <c r="H508" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I508" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="509" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="509" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C509" s="3">
         <v>507</v>
       </c>
       <c r="D509" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="E509" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F509" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="G509" s="5" t="s">
         <v>943</v>
       </c>
-      <c r="E509" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F509" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="G509" s="1" t="s">
-        <v>944</v>
-      </c>
       <c r="H509" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I509" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="510" spans="3:9" ht="72" x14ac:dyDescent="0.3">
@@ -20219,45 +20196,45 @@
         <v>508</v>
       </c>
       <c r="D510" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E510" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F510" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="G510" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="E510" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F510" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="G510" s="1" t="s">
-        <v>946</v>
-      </c>
       <c r="H510" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I510" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="511" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="511" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C511" s="3">
         <v>509</v>
       </c>
       <c r="D511" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="E511" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F511" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G511" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="E511" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F511" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="G511" s="1" t="s">
-        <v>948</v>
-      </c>
       <c r="H511" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I511" s="3">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="512" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -20265,22 +20242,22 @@
         <v>510</v>
       </c>
       <c r="D512" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="E512" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F512" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="G512" s="5" t="s">
         <v>949</v>
       </c>
-      <c r="E512" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F512" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="G512" s="5" t="s">
-        <v>950</v>
-      </c>
       <c r="H512" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I512" s="3">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="513" spans="3:9" ht="72" x14ac:dyDescent="0.3">
@@ -20288,71 +20265,71 @@
         <v>511</v>
       </c>
       <c r="D513" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="E513" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F513" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G513" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="E513" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F513" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="G513" s="5" t="s">
-        <v>952</v>
-      </c>
       <c r="H513" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I513" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="514" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="514" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C514" s="3">
         <v>512</v>
       </c>
       <c r="D514" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="E514" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F514" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="G514" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="E514" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F514" s="1" t="s">
-        <v>1200</v>
-      </c>
-      <c r="G514" s="1" t="s">
-        <v>954</v>
-      </c>
       <c r="H514" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I514" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="515" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="515" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C515" s="3">
         <v>513</v>
       </c>
       <c r="D515" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="E515" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="E515" s="1" t="s">
-        <v>886</v>
-      </c>
       <c r="F515" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="G515" s="5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G515" s="1" t="s">
         <v>956</v>
       </c>
       <c r="H515" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I515" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="516" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="516" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C516" s="9">
         <v>514</v>
       </c>
@@ -20360,10 +20337,10 @@
         <v>957</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>886</v>
+        <v>955</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>908</v>
+        <v>1195</v>
       </c>
       <c r="G516" s="1" t="s">
         <v>958</v>
@@ -20372,10 +20349,10 @@
         <v>6</v>
       </c>
       <c r="I516" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="517" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="517" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C517" s="3">
         <v>515</v>
       </c>
@@ -20383,10 +20360,10 @@
         <v>959</v>
       </c>
       <c r="E517" s="1" t="s">
-        <v>886</v>
+        <v>955</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>941</v>
+        <v>1196</v>
       </c>
       <c r="G517" s="1" t="s">
         <v>960</v>
@@ -20395,7 +20372,7 @@
         <v>6</v>
       </c>
       <c r="I517" s="3">
-        <v>62</v>
+        <v>26</v>
       </c>
     </row>
     <row r="518" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -20406,34 +20383,32 @@
         <v>961</v>
       </c>
       <c r="E518" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F518" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G518" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="F518" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="G518" s="1" t="s">
-        <v>963</v>
-      </c>
       <c r="H518" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I518" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="519" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="519" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C519" s="9">
         <v>517</v>
       </c>
       <c r="D519" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="E519" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="E519" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="F519" s="1" t="s">
-        <v>1202</v>
-      </c>
+      <c r="F519" s="1"/>
       <c r="G519" s="1" t="s">
         <v>965</v>
       </c>
@@ -20441,118 +20416,120 @@
         <v>6</v>
       </c>
       <c r="I519" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="520" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="520" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C520" s="3">
         <v>518</v>
       </c>
       <c r="D520" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E520" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="F520" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G520" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="E520" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="F520" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G520" s="1" t="s">
-        <v>967</v>
-      </c>
       <c r="H520" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I520" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="521" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="521" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C521" s="3">
         <v>519</v>
       </c>
       <c r="D521" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="E521" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="F521" s="1"/>
+      <c r="G521" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="E521" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="F521" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="G521" s="1" t="s">
-        <v>969</v>
-      </c>
       <c r="H521" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I521" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="522" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="522" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C522" s="9">
         <v>520</v>
       </c>
       <c r="D522" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="E522" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="F522" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G522" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="E522" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="F522" s="1"/>
-      <c r="G522" s="1" t="s">
-        <v>972</v>
-      </c>
       <c r="H522" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I522" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="523" spans="3:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="523" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C523" s="3">
         <v>521</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>609</v>
+        <v>971</v>
       </c>
       <c r="E523" s="1" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H523" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I523" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="524" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="524" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C524" s="3">
         <v>522</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E524" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="F524" s="1"/>
+        <v>964</v>
+      </c>
+      <c r="F524" s="1" t="s">
+        <v>1198</v>
+      </c>
       <c r="G524" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H524" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I524" s="3">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="525" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -20560,156 +20537,150 @@
         <v>523</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="F525" s="1" t="s">
-        <v>1205</v>
-      </c>
+        <v>964</v>
+      </c>
+      <c r="F525" s="1"/>
       <c r="G525" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H525" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I525" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="526" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="526" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C526" s="3">
         <v>524</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="E526" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="F526" s="1" t="s">
-        <v>1205</v>
-      </c>
+        <v>990</v>
+      </c>
+      <c r="F526" s="1"/>
       <c r="G526" s="1" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="H526" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I526" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="527" spans="3:9" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="527" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C527" s="3">
         <v>525</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
       <c r="E527" s="1" t="s">
-        <v>971</v>
+        <v>990</v>
       </c>
       <c r="F527" s="1" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>983</v>
+        <v>993</v>
       </c>
       <c r="H527" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I527" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="528" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="528" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C528" s="9">
         <v>526</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="F528" s="1"/>
+        <v>990</v>
+      </c>
+      <c r="F528" s="1" t="s">
+        <v>1202</v>
+      </c>
       <c r="G528" s="1" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="H528" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I528" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="529" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="529" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C529" s="3">
         <v>527</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="E529" s="1" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="F529" s="1"/>
       <c r="G529" s="1" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="H529" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I529" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="530" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="530" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C530" s="3">
         <v>528</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="E530" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="F530" s="1" t="s">
-        <v>1208</v>
-      </c>
+        <v>990</v>
+      </c>
+      <c r="F530" s="1"/>
       <c r="G530" s="1" t="s">
-        <v>1000</v>
+        <v>133</v>
       </c>
       <c r="H530" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I530" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="531" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="531" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C531" s="9">
         <v>529</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E531" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="F531" s="1" t="s">
-        <v>1209</v>
-      </c>
+        <v>990</v>
+      </c>
+      <c r="F531" s="1"/>
       <c r="G531" s="1" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="H531" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I531" s="3">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="532" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -20717,83 +20688,87 @@
         <v>530</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="F532" s="1"/>
       <c r="G532" s="1" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="H532" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I532" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="533" spans="3:9" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="533" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C533" s="3">
         <v>531</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E533" s="1" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="F533" s="1"/>
       <c r="G533" s="1" t="s">
-        <v>133</v>
+        <v>1003</v>
       </c>
       <c r="H533" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I533" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="534" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="534" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C534" s="9">
         <v>532</v>
       </c>
       <c r="D534" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E534" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="F534" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G534" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="E534" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="F534" s="1"/>
-      <c r="G534" s="1" t="s">
-        <v>1006</v>
-      </c>
       <c r="H534" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I534" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="535" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="535" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C535" s="3">
         <v>533</v>
       </c>
       <c r="D535" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E535" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="F535" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G535" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="E535" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="F535" s="1"/>
-      <c r="G535" s="1" t="s">
-        <v>1008</v>
-      </c>
       <c r="H535" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I535" s="3">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="536" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -20801,35 +20776,35 @@
         <v>534</v>
       </c>
       <c r="D536" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E536" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="F536" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G536" s="1" t="s">
         <v>1009</v>
       </c>
-      <c r="E536" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="F536" s="1"/>
-      <c r="G536" s="1" t="s">
-        <v>1010</v>
-      </c>
       <c r="H536" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I536" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="537" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="537" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C537" s="9">
         <v>535</v>
       </c>
       <c r="D537" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E537" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="E537" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="F537" s="1" t="s">
-        <v>1210</v>
-      </c>
+      <c r="F537" s="1"/>
       <c r="G537" s="1" t="s">
         <v>1012</v>
       </c>
@@ -20837,10 +20812,10 @@
         <v>6</v>
       </c>
       <c r="I537" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="538" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="538" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C538" s="3">
         <v>536</v>
       </c>
@@ -20848,11 +20823,9 @@
         <v>1013</v>
       </c>
       <c r="E538" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="F538" s="1" t="s">
-        <v>1208</v>
-      </c>
+        <v>1011</v>
+      </c>
+      <c r="F538" s="1"/>
       <c r="G538" s="1" t="s">
         <v>1014</v>
       </c>
@@ -20860,10 +20833,10 @@
         <v>6</v>
       </c>
       <c r="I538" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="539" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="539" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C539" s="3">
         <v>537</v>
       </c>
@@ -20871,11 +20844,9 @@
         <v>1015</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="F539" s="1" t="s">
-        <v>1211</v>
-      </c>
+        <v>1011</v>
+      </c>
+      <c r="F539" s="1"/>
       <c r="G539" s="1" t="s">
         <v>1016</v>
       </c>
@@ -20883,10 +20854,10 @@
         <v>6</v>
       </c>
       <c r="I539" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="540" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="540" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C540" s="9">
         <v>538</v>
       </c>
@@ -20894,112 +20865,112 @@
         <v>1017</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="F540" s="1"/>
       <c r="G540" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H540" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I540" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="541" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="541" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C541" s="3">
         <v>539</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E541" s="1" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="F541" s="1"/>
       <c r="G541" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H541" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I541" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="542" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="542" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C542" s="3">
         <v>540</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>1022</v>
+        <v>1208</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>1018</v>
+        <v>1209</v>
       </c>
       <c r="F542" s="1"/>
       <c r="G542" s="1" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
       <c r="H542" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I542" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="543" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="543" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C543" s="9">
         <v>541</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>1018</v>
+        <v>1209</v>
       </c>
       <c r="F543" s="1"/>
       <c r="G543" s="1" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="H543" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I543" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="544" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="544" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C544" s="3">
         <v>542</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>1018</v>
+        <v>1209</v>
       </c>
       <c r="F544" s="1"/>
       <c r="G544" s="1" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="H544" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I544" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="545" spans="3:9" ht="115.2" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="545" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C545" s="3">
         <v>543</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>1215</v>
+        <v>1038</v>
       </c>
       <c r="E545" s="1" t="s">
-        <v>1216</v>
+        <v>1039</v>
       </c>
       <c r="F545" s="1"/>
       <c r="G545" s="1" t="s">
@@ -21009,10 +20980,10 @@
         <v>6</v>
       </c>
       <c r="I545" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="546" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="546" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C546" s="9">
         <v>544</v>
       </c>
@@ -21020,7 +20991,7 @@
         <v>1041</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>1216</v>
+        <v>1039</v>
       </c>
       <c r="F546" s="1"/>
       <c r="G546" s="1" t="s">
@@ -21030,10 +21001,10 @@
         <v>6</v>
       </c>
       <c r="I546" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="547" spans="3:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="547" spans="3:9" ht="72" x14ac:dyDescent="0.3">
       <c r="C547" s="3">
         <v>545</v>
       </c>
@@ -21041,7 +21012,7 @@
         <v>1043</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>1216</v>
+        <v>1039</v>
       </c>
       <c r="F547" s="1"/>
       <c r="G547" s="1" t="s">
@@ -21051,94 +21022,96 @@
         <v>6</v>
       </c>
       <c r="I547" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="548" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="548" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C548" s="3">
         <v>546</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E548" s="1" t="s">
-        <v>1046</v>
+        <v>979</v>
+      </c>
+      <c r="E548" s="3" t="s">
+        <v>1199</v>
       </c>
       <c r="F548" s="1"/>
       <c r="G548" s="1" t="s">
-        <v>1047</v>
+        <v>980</v>
       </c>
       <c r="H548" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I548" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="549" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="549" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C549" s="9">
         <v>547</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E549" s="1" t="s">
-        <v>1046</v>
+        <v>979</v>
+      </c>
+      <c r="E549" s="3" t="s">
+        <v>1199</v>
       </c>
       <c r="F549" s="1"/>
       <c r="G549" s="1" t="s">
-        <v>1049</v>
+        <v>981</v>
       </c>
       <c r="H549" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I549" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="550" spans="3:9" ht="72" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="550" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C550" s="3">
         <v>548</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>1050</v>
-      </c>
-      <c r="E550" s="1" t="s">
-        <v>1046</v>
+        <v>982</v>
+      </c>
+      <c r="E550" s="3" t="s">
+        <v>1199</v>
       </c>
       <c r="F550" s="1"/>
       <c r="G550" s="1" t="s">
-        <v>1051</v>
+        <v>983</v>
       </c>
       <c r="H550" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I550" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="551" spans="3:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="551" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C551" s="3">
         <v>549</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="E551" s="3" t="s">
-        <v>1206</v>
-      </c>
-      <c r="F551" s="1"/>
+        <v>1199</v>
+      </c>
+      <c r="F551" s="1" t="s">
+        <v>1200</v>
+      </c>
       <c r="G551" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="H551" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I551" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="552" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="552" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C552" s="9">
         <v>550</v>
       </c>
@@ -21146,110 +21119,45 @@
         <v>986</v>
       </c>
       <c r="E552" s="3" t="s">
-        <v>1206</v>
-      </c>
-      <c r="F552" s="1"/>
+        <v>1199</v>
+      </c>
+      <c r="F552" s="1" t="s">
+        <v>1200</v>
+      </c>
       <c r="G552" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H552" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I552" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="553" spans="3:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="553" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C553" s="3">
         <v>551</v>
       </c>
-      <c r="D553" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="E553" s="3" t="s">
-        <v>1206</v>
+      <c r="D553" s="12" t="s">
+        <v>979</v>
+      </c>
+      <c r="E553" s="11" t="s">
+        <v>1199</v>
       </c>
       <c r="F553" s="1"/>
-      <c r="G553" s="1" t="s">
-        <v>990</v>
-      </c>
-      <c r="H553" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I553" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="554" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C554" s="3">
-        <v>552</v>
-      </c>
-      <c r="D554" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="E554" s="3" t="s">
-        <v>1206</v>
-      </c>
-      <c r="F554" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="G554" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="H554" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I554" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="555" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C555" s="9">
-        <v>553</v>
-      </c>
-      <c r="D555" s="1" t="s">
-        <v>993</v>
-      </c>
-      <c r="E555" s="3" t="s">
-        <v>1206</v>
-      </c>
-      <c r="F555" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="G555" s="1" t="s">
-        <v>994</v>
-      </c>
-      <c r="H555" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I555" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="556" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C556" s="3">
-        <v>554</v>
-      </c>
-      <c r="D556" s="12" t="s">
-        <v>986</v>
-      </c>
-      <c r="E556" s="11" t="s">
-        <v>1206</v>
-      </c>
-      <c r="F556" s="1"/>
-      <c r="G556" s="12" t="s">
-        <v>995</v>
-      </c>
-      <c r="H556" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I556" s="11">
+      <c r="G553" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="H553" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I553" s="11">
         <v>52</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H556" xr:uid="{113632FF-5A23-4E34-834C-C27100CE43A6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H553" xr:uid="{113632FF-5A23-4E34-834C-C27100CE43A6}">
       <formula1>"Factor,Construto teorico,Actor,Mecanismo/Proceso,Resultado/Consecuencia"</formula1>
     </dataValidation>
   </dataValidations>
